--- a/outputs/tables/tab-4-decomposicao.xlsx
+++ b/outputs/tables/tab-4-decomposicao.xlsx
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.03402268105564932</v>
+        <v>0.03962533169461402</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.06321452514711323</v>
+        <v>0.07313683556421191</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tab-4-decomposicao.xlsx
+++ b/outputs/tables/tab-4-decomposicao.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,7 +362,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pseudo_r2</t>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mcfadden</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>aic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bic</t>
         </is>
       </c>
     </row>
@@ -373,17 +393,63 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.03962533169461402</v>
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>0.04353723526704389</v>
+      </c>
+      <c r="D2">
+        <v>0.04323659421051618</v>
+      </c>
+      <c r="E2">
+        <v>57283.39802658442</v>
+      </c>
+      <c r="F2">
+        <v>57366.29089979897</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unidade da USP (48 categorias)</t>
+          <t>Unidade de ingresso (48 categorias)</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.07313683556421191</v>
+        <v>47</v>
+      </c>
+      <c r="C3">
+        <v>0.07925972704991335</v>
+      </c>
+      <c r="D3">
+        <v>0.0776897126436018</v>
+      </c>
+      <c r="E3">
+        <v>55220.6187809349</v>
+      </c>
+      <c r="F3">
+        <v>55653.50378549972</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Características do estudante</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>0.05665716680253108</v>
+      </c>
+      <c r="D4">
+        <v>0.05612269381314849</v>
+      </c>
+      <c r="E4">
+        <v>56511.8806712162</v>
+      </c>
+      <c r="F4">
+        <v>56659.24577915316</v>
       </c>
     </row>
   </sheetData>
